--- a/Plantillas/PlantillaDocumentaciónMER.xlsx
+++ b/Plantillas/PlantillaDocumentaciónMER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luciana\Downloads\OneDrive_2024-01-30\Sesión 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="592" documentId="13_ncr:1_{DA4F7EDE-002B-447A-9232-E45CAE8BFCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CCADC5D-12D2-44CD-BB6D-CCE6170E7DC8}"/>
+  <xr:revisionPtr revIDLastSave="675" documentId="13_ncr:1_{DA4F7EDE-002B-447A-9232-E45CAE8BFCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E165772-5AB8-4D6F-A29C-101305E5CEEA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" firstSheet="5" activeTab="5" xr2:uid="{59653BFD-5B7C-4315-9D96-3FD5833491E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" firstSheet="11" activeTab="11" xr2:uid="{59653BFD-5B7C-4315-9D96-3FD5833491E5}"/>
   </bookViews>
   <sheets>
     <sheet name="MER" sheetId="1" r:id="rId1"/>
@@ -18,22 +18,32 @@
     <sheet name="Departamento" sheetId="3" r:id="rId3"/>
     <sheet name="Valores" sheetId="4" state="hidden" r:id="rId4"/>
     <sheet name="Ciudad" sheetId="7" r:id="rId5"/>
-    <sheet name="Cliente" sheetId="8" r:id="rId6"/>
+    <sheet name="Usuario" sheetId="8" r:id="rId6"/>
     <sheet name="Colaborador" sheetId="5" r:id="rId7"/>
     <sheet name="Negocio" sheetId="10" r:id="rId8"/>
     <sheet name="Sede" sheetId="9" r:id="rId9"/>
     <sheet name="Solicitud de Cotizacion" sheetId="6" r:id="rId10"/>
     <sheet name="Producto" sheetId="12" r:id="rId11"/>
-    <sheet name="Cotizacion" sheetId="11" r:id="rId12"/>
+    <sheet name="Transaccion de Pago" sheetId="15" r:id="rId12"/>
+    <sheet name="Plan de Suscripcion" sheetId="14" r:id="rId13"/>
+    <sheet name="Notificacion" sheetId="13" r:id="rId14"/>
+    <sheet name="Cotizacion" sheetId="11" r:id="rId15"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId16"/>
+    <externalReference r:id="rId17"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Ciudad!$A$5:$A$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Cliente!$A$5:$A$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Usuario!$A$5:$A$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Colaborador!$A$5:$A$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Cotizacion!$A$5:$A$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Producto!$A$5:$A$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">Cotizacion!$A$5:$A$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Departamento!$A$5:$A$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Negocio!$A$5:$A$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">Notificacion!$A$5:$A$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Plan de Suscripcion'!$A$5:$A$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Transaccion de Pago'!$A$5:$A$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Producto!$A$5:$A$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Sede!$A$5:$A$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Solicitud de Cotizacion'!$A$5:$A$6</definedName>
   </definedNames>
@@ -58,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="303">
   <si>
     <t>Entidad</t>
   </si>
@@ -78,7 +88,7 @@
     <t>Entidad que contiene la información de la ciudad donde reside el cliente y/o donde está ubicado su negocio</t>
   </si>
   <si>
-    <t>Cliente</t>
+    <t>Usuario</t>
   </si>
   <si>
     <t>Entidad que contiene la información del usuario que realiza las solicitudes de cotización en la aplicación</t>
@@ -120,6 +130,24 @@
     <t>Entidad que contiene la información de la respuesta que da el proveedor a la solicitud de cotización del cliente</t>
   </si>
   <si>
+    <t>Notificación</t>
+  </si>
+  <si>
+    <t>Entidad que contiene la información de las notificaciones que recibe el usuario dentro de la aplicación</t>
+  </si>
+  <si>
+    <t>Plan de suscripcion</t>
+  </si>
+  <si>
+    <t>Entidad que contiene la información de los planes de suscripcion que el usuario puede obtener</t>
+  </si>
+  <si>
+    <t>Transaccion de pago</t>
+  </si>
+  <si>
+    <t>Entidad que contiene la información de las transacciones de pago que tiene el usuario para adquirir un plan de suscripción</t>
+  </si>
+  <si>
     <t>&lt;-Volver al inicio</t>
   </si>
   <si>
@@ -288,274 +316,667 @@
     <t>id</t>
   </si>
   <si>
-    <t>UQ_IdentificacionCliente</t>
-  </si>
-  <si>
-    <t>IDX_IdentificacionCliente_ASC</t>
-  </si>
-  <si>
-    <t>Identificación única del cliente.</t>
-  </si>
-  <si>
-    <t>IDX_NombreCliente_ASC</t>
-  </si>
-  <si>
-    <t>Nombre del cliente.</t>
-  </si>
-  <si>
-    <t>apellido</t>
-  </si>
-  <si>
-    <t>IDX_ApellidoCliente_ASC</t>
-  </si>
-  <si>
-    <t>Apellido del cliente.</t>
-  </si>
-  <si>
-    <t>correo</t>
-  </si>
-  <si>
-    <t>UQ_CorreoCliente</t>
-  </si>
-  <si>
-    <t>IDX_CorreoCliente_ASC</t>
-  </si>
-  <si>
-    <t>Correo electrónico del cliente.</t>
-  </si>
-  <si>
-    <t>contraseña</t>
-  </si>
-  <si>
-    <t>IDX_ContraseñaCliente_ASC</t>
-  </si>
-  <si>
-    <t>Contraseña del cliente para el inicio de sesión.</t>
-  </si>
-  <si>
-    <t>CIUDAD</t>
-  </si>
-  <si>
-    <t>IDX_CodigoCiudadCliente_ASC</t>
-  </si>
-  <si>
-    <t>Código de la ciudad donde reside el cliente.</t>
-  </si>
-  <si>
-    <t>identificacion</t>
-  </si>
-  <si>
-    <t>UQ_identificacion_colaborador</t>
-  </si>
-  <si>
-    <t>IDX_identificacion_colaborador</t>
-  </si>
-  <si>
-    <t>Identificación única del colaborador.</t>
-  </si>
-  <si>
-    <t>cliente</t>
-  </si>
-  <si>
-    <t>CLIENTE</t>
-  </si>
-  <si>
-    <t>IDX_identificacion_cliente_colaborador</t>
-  </si>
-  <si>
-    <t>Identificación del cliente asociado al colaborador.</t>
-  </si>
-  <si>
-    <t>UQ_correo_colaborador</t>
-  </si>
-  <si>
-    <t>IDX_correo_colaborador</t>
-  </si>
-  <si>
-    <t>Correo electrónico del colaborador.</t>
-  </si>
-  <si>
-    <t>estado_invitacion</t>
+    <t>UUID</t>
+  </si>
+  <si>
+    <t>IDX_PK_Users</t>
+  </si>
+  <si>
+    <t>BTREE</t>
+  </si>
+  <si>
+    <t>ID Usuario</t>
+  </si>
+  <si>
+    <t>Identificador único universal del usuario.</t>
+  </si>
+  <si>
+    <t>identification</t>
+  </si>
+  <si>
+    <t>UQ_Users_Identif</t>
+  </si>
+  <si>
+    <t>IDX_Users_Identif</t>
+  </si>
+  <si>
+    <t>Identificación</t>
+  </si>
+  <si>
+    <t>Número de documento o identificación legal.</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>IDX_Users_Name</t>
+  </si>
+  <si>
+    <t>Nombres</t>
+  </si>
+  <si>
+    <t>Nombres de pila del usuario.</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>IDX_Users_LastName</t>
+  </si>
+  <si>
+    <t>Apellidos</t>
+  </si>
+  <si>
+    <t>Apellidos del usuario</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>UQ_Users_Email</t>
+  </si>
+  <si>
+    <t>IDX_Users_Email</t>
+  </si>
+  <si>
+    <t>Correo Electrónico</t>
+  </si>
+  <si>
+    <t>Email y nombre de usuario para el acceso.</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>Contraseña</t>
+  </si>
+  <si>
+    <t>Contraseña cifrada (Bcrypt hash).</t>
+  </si>
+  <si>
+    <t>department</t>
+  </si>
+  <si>
+    <t>Departamento de ubicación del usuario.</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>Ciudad de ubicación del usuario.</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>ENUM</t>
+  </si>
+  <si>
+    <t>Rol</t>
+  </si>
+  <si>
+    <t>Rol en el sistema (OWNER o COLLABORATOR).</t>
+  </si>
+  <si>
+    <t>ownerId</t>
+  </si>
+  <si>
+    <t>IDX_Users_Owner</t>
+  </si>
+  <si>
+    <t>ID Propietario</t>
+  </si>
+  <si>
+    <t>Referencia al dueño si es colaborador.</t>
+  </si>
+  <si>
+    <t>planId</t>
+  </si>
+  <si>
+    <t>IDX_Users_Plan</t>
+  </si>
+  <si>
+    <t>ID Plan</t>
+  </si>
+  <si>
+    <t>Referencia al plan de suscripción del usuario.</t>
+  </si>
+  <si>
+    <t>planStartDate</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>Fecha Inicio Plan</t>
+  </si>
+  <si>
+    <t>Fecha de activación de la suscripción.</t>
+  </si>
+  <si>
+    <t>IDX_PK_Collab</t>
+  </si>
+  <si>
+    <t>ID Colaborador</t>
+  </si>
+  <si>
+    <t>Identificador único del registro de colaborador.</t>
+  </si>
+  <si>
+    <t>IDX_Collab_Email</t>
+  </si>
+  <si>
+    <t>Email al que se envió la invitación.</t>
+  </si>
+  <si>
+    <t>invitationStatus</t>
+  </si>
+  <si>
+    <t>Estado Invitación</t>
+  </si>
+  <si>
+    <t>PENDING, ACCEPTED o REJECTED.</t>
+  </si>
+  <si>
+    <t>userId</t>
+  </si>
+  <si>
+    <t>users</t>
+  </si>
+  <si>
+    <t>IDX_Collab_User</t>
+  </si>
+  <si>
+    <t>El usuario (Owner) que invita al colaborador.</t>
+  </si>
+  <si>
+    <t>createdAt</t>
+  </si>
+  <si>
+    <t>Fecha Creación</t>
+  </si>
+  <si>
+    <t>Fecha en la que se creó el registro.</t>
+  </si>
+  <si>
+    <t>IDX_PK_Business</t>
+  </si>
+  <si>
+    <t>ID Negocio</t>
+  </si>
+  <si>
+    <t>Identificador único del negocio.</t>
+  </si>
+  <si>
+    <t>nit</t>
+  </si>
+  <si>
+    <t>UQ_Business_NIT</t>
+  </si>
+  <si>
+    <t>IDX_Business_NIT</t>
+  </si>
+  <si>
+    <t>NIT</t>
+  </si>
+  <si>
+    <t>Número de identificación tributaria.</t>
+  </si>
+  <si>
+    <t>IDX_Business_Name</t>
+  </si>
+  <si>
+    <t>Nombre comercial del negocio.</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Breve descripción de la actividad.</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>Dirección</t>
+  </si>
+  <si>
+    <t>Ubicación física principal del negocio.</t>
+  </si>
+  <si>
+    <t>IDX_Business_User</t>
+  </si>
+  <si>
+    <t>ID Cliente</t>
+  </si>
+  <si>
+    <t>Referencia al usuario dueño del negocio.</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>PENDIENTE, VERIFICADO o RECHAZADO.</t>
+  </si>
+  <si>
+    <t>rutUrl</t>
+  </si>
+  <si>
+    <t>URL RUT</t>
+  </si>
+  <si>
+    <t>Enlace al documento RUT cargado.</t>
+  </si>
+  <si>
+    <t>chamberOfCommerceUrl</t>
+  </si>
+  <si>
+    <t>URL Cámara Com.</t>
+  </si>
+  <si>
+    <t>Enlace al certificado de existencia.</t>
+  </si>
+  <si>
+    <t>IDX_PK_Branch</t>
+  </si>
+  <si>
+    <t>ID Sede</t>
+  </si>
+  <si>
+    <t>Identificador único de la sede.</t>
+  </si>
+  <si>
+    <t>UQ_Branch_Name</t>
+  </si>
+  <si>
+    <t>IDX_Branch_Name</t>
+  </si>
+  <si>
+    <t>Nombre identificativo de la sede.</t>
+  </si>
+  <si>
+    <t>Dirección física de la sede.</t>
+  </si>
+  <si>
+    <t>Ciudad donde se ubica la sede.</t>
+  </si>
+  <si>
+    <t>businessId</t>
+  </si>
+  <si>
+    <t>businesses</t>
+  </si>
+  <si>
+    <t>IDX_Branch_Business</t>
+  </si>
+  <si>
+    <t>Referencia al negocio al que pertenece la sede.</t>
+  </si>
+  <si>
+    <t>IDX_PK_QReq</t>
+  </si>
+  <si>
+    <t>ID Solicitud</t>
+  </si>
+  <si>
+    <t>Identificador único de la solicitud.</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>IDX_QReq_Title</t>
+  </si>
+  <si>
+    <t>Título</t>
+  </si>
+  <si>
+    <t>Breve título de la solicitud de cotización.</t>
+  </si>
+  <si>
+    <t>Detalle extenso de lo que se solicita.</t>
+  </si>
+  <si>
+    <t>Fecha y hora en que se creó la solicitud.</t>
+  </si>
+  <si>
+    <t>responseDeadline</t>
+  </si>
+  <si>
+    <t>Fecha Límite</t>
+  </si>
+  <si>
+    <t>Fecha máxima para recibir ofertas.</t>
+  </si>
+  <si>
+    <t>DRAFT, PENDING, QUOTED, EXPIRED, CLOSED.</t>
+  </si>
+  <si>
+    <t>IDX_QReq_User</t>
+  </si>
+  <si>
+    <t>Referencia al usuario que solicita.</t>
+  </si>
+  <si>
+    <t>branchId</t>
+  </si>
+  <si>
+    <t>branches</t>
+  </si>
+  <si>
+    <t>IDX_QReq_Branch</t>
+  </si>
+  <si>
+    <t>Referencia a la sede de la solicitud.</t>
+  </si>
+  <si>
+    <t>IDX_PK_Product</t>
+  </si>
+  <si>
+    <t>ID Producto</t>
+  </si>
+  <si>
+    <t>Identificador único del producto.</t>
+  </si>
+  <si>
+    <t>IDX_Prod_Name</t>
+  </si>
+  <si>
+    <t>Nombre del producto.</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>CHK_Prod_Amount</t>
+  </si>
+  <si>
+    <t>Cantidad</t>
+  </si>
+  <si>
+    <t>Cantidad de unidades solicitadas.</t>
+  </si>
+  <si>
+    <t>unitOfMeasurement</t>
+  </si>
+  <si>
+    <t>Unidad Medida</t>
+  </si>
+  <si>
+    <t>Unidad de medida (kg, litros, etc.).</t>
+  </si>
+  <si>
+    <t>Detalle adicional del producto.</t>
+  </si>
+  <si>
+    <t>quotationRequestId</t>
+  </si>
+  <si>
+    <t>quotation_requests</t>
+  </si>
+  <si>
+    <t>IDX_Prod_QReq</t>
+  </si>
+  <si>
+    <t>Referencia a la solicitud de cotización.</t>
+  </si>
+  <si>
+    <t>Fecha en que se agregó el producto.</t>
+  </si>
+  <si>
+    <t>IDX_PK_Payment</t>
+  </si>
+  <si>
+    <t>ID Transacción</t>
+  </si>
+  <si>
+    <t>Identificador único de la transacción en el sistema.</t>
+  </si>
+  <si>
+    <t>IDX_Pay_User</t>
+  </si>
+  <si>
+    <t>Referencia al usuario que realiza el pago.</t>
+  </si>
+  <si>
+    <t>plans</t>
+  </si>
+  <si>
+    <t>IDX_Pay_Plan</t>
+  </si>
+  <si>
+    <t>Referencia al plan que se está adquiriendo.</t>
+  </si>
+  <si>
+    <t>Monto</t>
+  </si>
+  <si>
+    <t>Valor total pagado por la suscripción.</t>
+  </si>
+  <si>
+    <t>Estado Pago</t>
+  </si>
+  <si>
+    <t>PENDIENTE, APROBADO, RECHAZADO, etc.</t>
+  </si>
+  <si>
+    <t>wompiId</t>
+  </si>
+  <si>
+    <t>IDX_Pay_Wompi</t>
+  </si>
+  <si>
+    <t>Ref. Wompi</t>
+  </si>
+  <si>
+    <t>ID de referencia devuelto por la pasarela Wompi.</t>
+  </si>
+  <si>
+    <t>Fecha Pago</t>
+  </si>
+  <si>
+    <t>Fecha y hora en que se registró la transacción.</t>
+  </si>
+  <si>
+    <t>IDX_PK_Plan</t>
+  </si>
+  <si>
+    <t>Identificador único del plan.</t>
+  </si>
+  <si>
+    <t>UQ_Plan_Name</t>
+  </si>
+  <si>
+    <t>IDX_Plan_Name</t>
+  </si>
+  <si>
+    <t>Nombre Plan</t>
+  </si>
+  <si>
+    <t>Nombre descriptivo del plan</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>Precio</t>
+  </si>
+  <si>
+    <t>Costo mensual de la suscripción.</t>
+  </si>
+  <si>
+    <t>requestLimit</t>
+  </si>
+  <si>
+    <t>Límite Solicitudes</t>
+  </si>
+  <si>
+    <t>Cantidad máxima de solicitudes permitidas.</t>
+  </si>
+  <si>
+    <t>quotationLimit</t>
+  </si>
+  <si>
+    <t>Límite Ofertas</t>
+  </si>
+  <si>
+    <t>Cantidad máxima de ofertas que puede recibir.</t>
+  </si>
+  <si>
+    <t>collaboratorLimit</t>
+  </si>
+  <si>
+    <t>Límite Colab.</t>
+  </si>
+  <si>
+    <t>Máximo de colaboradores permitidos.</t>
+  </si>
+  <si>
+    <t>IDX_PK_Notification</t>
+  </si>
+  <si>
+    <t>ID Notificación</t>
+  </si>
+  <si>
+    <t>Identificador único de la notificación.</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Tipo Mensaje</t>
+  </si>
+  <si>
+    <t>TRANSACTIONAL, SYSTEM o TEAM.</t>
+  </si>
+  <si>
+    <t>Título corto de la notificación.</t>
+  </si>
+  <si>
+    <t>message</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>Mensaje</t>
+  </si>
+  <si>
+    <t>Contenido detallado de la notificación.</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>Enlace</t>
+  </si>
+  <si>
+    <t>URL para redireccionar al usuario al hacer clic.</t>
+  </si>
+  <si>
+    <t>isRead</t>
   </si>
   <si>
     <t>BOOLEAN</t>
   </si>
   <si>
-    <t>Indica si el colaborador ha aceptado la invitación para formar parte del sistema.</t>
-  </si>
-  <si>
-    <t>nit</t>
-  </si>
-  <si>
-    <t>IDX_negocio_nit</t>
-  </si>
-  <si>
-    <t>Número de identificación tributaria del negocio.</t>
-  </si>
-  <si>
-    <t>UQ_negocio_nombre</t>
-  </si>
-  <si>
-    <t>Nombre del negocio.</t>
-  </si>
-  <si>
-    <t>descripcion</t>
-  </si>
-  <si>
-    <t>Descripción del negocio.</t>
-  </si>
-  <si>
-    <t>direccion</t>
-  </si>
-  <si>
-    <t>Dirección física del negocio.</t>
-  </si>
-  <si>
-    <t>identificación</t>
-  </si>
-  <si>
-    <t>Referencia al cliente asociado al negocio.</t>
-  </si>
-  <si>
-    <t>codigo</t>
-  </si>
-  <si>
-    <t>IDX_sede_id</t>
-  </si>
-  <si>
-    <t>Identificador único de la sede.</t>
-  </si>
-  <si>
-    <t>UQ_sede_nombre</t>
-  </si>
-  <si>
-    <t>Nombre de la sede.</t>
-  </si>
-  <si>
-    <t>Dirección física de la sede.</t>
-  </si>
-  <si>
-    <t>negocio</t>
-  </si>
-  <si>
-    <t>Referencia al negocio al que pertenece la sede.</t>
-  </si>
-  <si>
-    <t>ciudad</t>
-  </si>
-  <si>
-    <t>id_ciudad</t>
-  </si>
-  <si>
-    <t>Referencia a la ciudad donde se encuentra la sede.</t>
-  </si>
-  <si>
-    <t>IDX_solicitud_codigo</t>
-  </si>
-  <si>
-    <t>Identificador único de la solicitud de cotización.</t>
-  </si>
-  <si>
-    <t>fecha_creacion</t>
-  </si>
-  <si>
-    <t>DATE</t>
-  </si>
-  <si>
-    <t>Fecha en la que se creó la solicitud de cotización.</t>
-  </si>
-  <si>
-    <t>fecha_limite_respuesta</t>
-  </si>
-  <si>
-    <t>Fecha límite para que la solicitud sea respondida.</t>
-  </si>
-  <si>
-    <t>estado_solicitud</t>
-  </si>
-  <si>
-    <t>CHK_estado_solicitud</t>
-  </si>
-  <si>
-    <t>Estado de la solicitud (ej. Pendiente, Aprobada, Rechazada).</t>
-  </si>
-  <si>
-    <t>Referencia al cliente que realizó la solicitud.</t>
-  </si>
-  <si>
-    <t>sede</t>
-  </si>
-  <si>
-    <t>Referencia a la sede donde se realizó la solicitud.</t>
-  </si>
-  <si>
-    <t>IDX_producto_codigo</t>
-  </si>
-  <si>
-    <t>Identificador único del producto.</t>
-  </si>
-  <si>
-    <t>UQ_producto_nombre</t>
-  </si>
-  <si>
-    <t>IDX_producto_nombre</t>
-  </si>
-  <si>
-    <t>Nombre del producto.</t>
-  </si>
-  <si>
-    <t>cantidad</t>
-  </si>
-  <si>
-    <t>CHK_producto_cantidad</t>
-  </si>
-  <si>
-    <t>Cantidad de unidades del producto en la solicitud.</t>
-  </si>
-  <si>
-    <t>unidad_medida</t>
-  </si>
-  <si>
-    <t>Unidad de medida para el producto (ej. kg, litros, etc.).</t>
-  </si>
-  <si>
-    <t>Descripción detallada del producto.</t>
-  </si>
-  <si>
-    <t>IDX_cotizacion_codigo</t>
+    <t>¿Leído?</t>
+  </si>
+  <si>
+    <t>SI si el usuario ya vio la notificación, NO si no.</t>
+  </si>
+  <si>
+    <t>Fecha y hora en que se envió la notificación.</t>
+  </si>
+  <si>
+    <t>IDX_Notif_User</t>
+  </si>
+  <si>
+    <t>ID Destinatario</t>
+  </si>
+  <si>
+    <t>Referencia al usuario que recibe el mensaje.</t>
+  </si>
+  <si>
+    <t>IDX_PK_Quotation</t>
+  </si>
+  <si>
+    <t>ID Cotización</t>
   </si>
   <si>
     <t>Identificador único de la cotización.</t>
   </si>
   <si>
-    <t>fecha_emision</t>
-  </si>
-  <si>
-    <t>Fecha en la que se generó la cotización.</t>
-  </si>
-  <si>
-    <t>fecha_expiracion</t>
-  </si>
-  <si>
-    <t>Fecha límite para que la cotización sea válida.</t>
-  </si>
-  <si>
-    <t>Descripción adicional sobre la cotización.</t>
-  </si>
-  <si>
-    <t>tiempo_entrega</t>
-  </si>
-  <si>
-    <t>Tiempo estimado de entrega de los productos o servicios cotizados.</t>
-  </si>
-  <si>
-    <t>solicitud</t>
-  </si>
-  <si>
-    <t>Solicitud_Cotizacion</t>
-  </si>
-  <si>
-    <t>Referencia a la solicitud de cotización asociada.</t>
+    <t>issueDate</t>
+  </si>
+  <si>
+    <t>Fecha Emisión</t>
+  </si>
+  <si>
+    <t>Fecha y hora de generación de la cotización.</t>
+  </si>
+  <si>
+    <t>deliveryTime</t>
+  </si>
+  <si>
+    <t>Tiempo Entrega</t>
+  </si>
+  <si>
+    <t>Fecha estimada de entrega de los productos.</t>
+  </si>
+  <si>
+    <t>Fecha Expiración</t>
+  </si>
+  <si>
+    <t>Fecha límite de validez de la oferta.</t>
+  </si>
+  <si>
+    <t>DECIMAL</t>
+  </si>
+  <si>
+    <t>CHK_Quot_Price</t>
+  </si>
+  <si>
+    <t>Valor Total</t>
+  </si>
+  <si>
+    <t>Monto total de la cotización.</t>
+  </si>
+  <si>
+    <t>Comentarios adicionales del proveedor.</t>
+  </si>
+  <si>
+    <t>DRAFT, PENDING, ACCEPTED, EXPIRED.</t>
+  </si>
+  <si>
+    <t>individualValues</t>
+  </si>
+  <si>
+    <t>JSON</t>
+  </si>
+  <si>
+    <t>Desglose Items</t>
+  </si>
+  <si>
+    <t>Detalle de valores por producto (en formato JSON).</t>
+  </si>
+  <si>
+    <t>IDX_Quot_Request</t>
+  </si>
+  <si>
+    <t>Referencia a la solicitud que se responde.</t>
+  </si>
+  <si>
+    <t>IDX_Quot_User</t>
+  </si>
+  <si>
+    <t>ID Proveedor</t>
+  </si>
+  <si>
+    <t>Usuario que emite la cotización.</t>
   </si>
 </sst>
 </file>
@@ -962,22 +1383,25 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
+        <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55EFC9FE-C61B-0F3D-B0AD-BC31CDAF2B9B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAE3843A-6F99-DC88-3B30-81072A4557B3}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{55EFC9FE-C61B-0F3D-B0AD-BC31CDAF2B9B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -993,8 +1417,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="600075" y="133350"/>
-          <a:ext cx="5057775" cy="5467350"/>
+          <a:off x="0" y="200025"/>
+          <a:ext cx="10896600" cy="8753475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1004,6 +1428,32 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="EntidaUno"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Clases"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1317,7 +1767,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98B87756-89E0-463F-8FBF-BE46A89C028E}">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1345,7 +1795,7 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1380,7 +1830,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -1404,52 +1854,52 @@
     </row>
     <row r="5" spans="1:20" s="4" customFormat="1">
       <c r="A5" s="27" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
       <c r="S5" s="17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="4" customFormat="1">
@@ -1462,355 +1912,536 @@
       <c r="G6" s="17"/>
       <c r="H6" s="22"/>
       <c r="I6" s="14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>0</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="16" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>47</v>
+        <v>82</v>
+      </c>
+      <c r="C7" s="15">
+        <v>36</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>182</v>
+      </c>
       <c r="N7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="S7" s="15"/>
+        <v>182</v>
+      </c>
+      <c r="S7" s="15" t="s">
+        <v>183</v>
+      </c>
       <c r="T7" s="15" t="s">
-        <v>131</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="16" t="s">
-        <v>132</v>
+        <v>185</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>47</v>
+        <v>60</v>
+      </c>
+      <c r="C8" s="15">
+        <v>150</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q8" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>84</v>
+      </c>
       <c r="R8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S8" s="15"/>
+        <v>186</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>187</v>
+      </c>
       <c r="T8" s="15" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="16" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>47</v>
+        <v>60</v>
+      </c>
+      <c r="C9" s="15">
+        <v>500</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="R9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S9" s="15"/>
+        <v>53</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>154</v>
+      </c>
       <c r="T9" s="15" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="16" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="15">
-        <v>20</v>
+        <v>125</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N10" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="P10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="R10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S10" s="15"/>
+        <v>53</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>141</v>
+      </c>
       <c r="T10" s="15" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="16" t="s">
-        <v>98</v>
+        <v>191</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="R11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S11" s="15"/>
+        <v>53</v>
+      </c>
+      <c r="S11" s="15" t="s">
+        <v>192</v>
+      </c>
       <c r="T11" s="15" t="s">
-        <v>140</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="16" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M12" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O12" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q12" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q12" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="R12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S12" s="15"/>
+        <v>53</v>
+      </c>
+      <c r="S12" s="15" t="s">
+        <v>65</v>
+      </c>
       <c r="T12" s="15" t="s">
-        <v>142</v>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="15">
+        <v>36</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q13" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R13" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="S13" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="T13" s="15" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="15">
+        <v>36</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q14" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R14" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="S14" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="T14" s="15" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:K5"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="P5:R5"/>
@@ -1826,35 +2457,20 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="S5:S6"/>
     <mergeCell ref="T5:T6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1:E1" location="Clases!A1" display="&lt;-Volver al inicio" xr:uid="{ECC1C620-46F4-42E9-82C0-2BB03750EF38}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9BFBD7C6-1117-435F-8517-2E6C0385E28F}">
-          <x14:formula1>
-            <xm:f>Valores!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>N7:N12 F7:I12 L7:L12 P7:P12 R8:R12</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{44D85C4F-2651-4D65-BA8B-CA701B777CBF}">
-          <x14:formula1>
-            <xm:f>Valores!$D$2:$D$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q7:Q12</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1775AAED-3440-441C-8C50-5FB04B250FB6}">
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1882,7 +2498,7 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1917,7 +2533,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -1941,52 +2557,52 @@
     </row>
     <row r="5" spans="1:20" s="4" customFormat="1">
       <c r="A5" s="17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
       <c r="S5" s="17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="4" customFormat="1">
@@ -1999,297 +2615,474 @@
       <c r="G6" s="17"/>
       <c r="H6" s="22"/>
       <c r="I6" s="14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>0</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="15" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>47</v>
+        <v>82</v>
+      </c>
+      <c r="C7" s="15">
+        <v>36</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>201</v>
+      </c>
       <c r="N7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="S7" s="15"/>
+        <v>201</v>
+      </c>
+      <c r="S7" s="15" t="s">
+        <v>202</v>
+      </c>
       <c r="T7" s="15" t="s">
-        <v>144</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="15" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C8" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L8" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="S8" s="15"/>
+        <v>204</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="T8" s="15" t="s">
-        <v>147</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="15" t="s">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
+      </c>
+      <c r="D9" s="15">
+        <v>10</v>
+      </c>
+      <c r="E9" s="15">
+        <v>0</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N9" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="O9" s="15" t="s">
-        <v>149</v>
+        <v>207</v>
       </c>
       <c r="P9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="R9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S9" s="15"/>
+        <v>53</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>208</v>
+      </c>
       <c r="T9" s="15" t="s">
-        <v>150</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="15" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C10" s="15">
         <v>50</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>211</v>
+      </c>
       <c r="T10" s="15" t="s">
-        <v>152</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="15" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C11" s="15">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S11" s="15" t="s">
+        <v>154</v>
+      </c>
       <c r="T11" s="15" t="s">
-        <v>153</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="15">
+        <v>36</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q12" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R12" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="S12" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="T12" s="15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S13" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="T13" s="15" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:K5"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="P5:R5"/>
@@ -2305,34 +3098,660 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="S5:S6"/>
     <mergeCell ref="T5:T6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1:E1" location="Clases!A1" display="&lt;-Volver al inicio" xr:uid="{D0EF66DD-8A16-4441-9913-3F0262AEDA63}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E279736A-9A09-4208-B16C-C6A0AB3B2F85}">
-          <x14:formula1>
-            <xm:f>Valores!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>N7:N11 F7:I11 L7:L11 P7:P11 R9:R11</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2E1C4106-6FC9-4758-926E-D6A5764A21C3}">
-          <x14:formula1>
-            <xm:f>Valores!$D$2:$D$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q7:Q11</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6126429D-1B10-43E4-A762-EE4E3AFC7A2B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B3BCC55-4F5C-4DE0-B486-5E100D565FBE}">
+  <dimension ref="A1:T13"/>
+  <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="61.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="19.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="A1" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A2" s="2" t="str">
+        <f>Entidades!$A$1</f>
+        <v>Entidad</v>
+      </c>
+      <c r="B2" s="23" t="str">
+        <f>Entidades!A10</f>
+        <v>Cotizacion</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="24"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="3" t="str">
+        <f>Entidades!$B$1</f>
+        <v>Desripción</v>
+      </c>
+      <c r="B3" s="25" t="str">
+        <f>Entidades!B10</f>
+        <v>Entidad que contiene la información de la respuesta que da el proveedor a la solicitud de cotización del cliente</v>
+      </c>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="21"/>
+    </row>
+    <row r="5" spans="1:20" s="4" customFormat="1">
+      <c r="A5" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="T5" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="4" customFormat="1">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q6" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="15">
+        <v>36</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q7" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="S7" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="T7" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="15">
+        <v>36</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R8" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="T8" s="15" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="15">
+        <v>36</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P9" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="T9" s="15" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="15">
+        <v>10</v>
+      </c>
+      <c r="E10" s="15">
+        <v>0</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="T10" s="15" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="15">
+        <v>20</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S11" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="T11" s="15" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="15">
+        <v>100</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q12" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R12" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="S12" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="T12" s="15" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S13" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="T13" s="15" t="s">
+        <v>236</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A4:T4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:R5"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:E1" location="Clases!A1" display="&lt;-Volver al inicio" xr:uid="{D67C7CCB-AB25-46D9-BC12-56E9A5289A3F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{908429CE-4316-428F-B84F-5848715F4F9F}">
   <dimension ref="A1:T12"/>
   <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15"/>
   <cols>
@@ -2361,7 +3780,7 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -2396,7 +3815,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -2420,52 +3839,52 @@
     </row>
     <row r="5" spans="1:20" s="4" customFormat="1">
       <c r="A5" s="17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
       <c r="S5" s="17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="4" customFormat="1">
@@ -2478,345 +3897,1940 @@
       <c r="G6" s="17"/>
       <c r="H6" s="22"/>
       <c r="I6" s="14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>0</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="15" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>47</v>
+        <v>82</v>
+      </c>
+      <c r="C7" s="15">
+        <v>36</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>237</v>
+      </c>
       <c r="N7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="S7" s="15"/>
+        <v>237</v>
+      </c>
+      <c r="S7" s="15" t="s">
+        <v>122</v>
+      </c>
       <c r="T7" s="15" t="s">
-        <v>155</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="15" t="s">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>47</v>
+        <v>60</v>
+      </c>
+      <c r="C8" s="15">
+        <v>50</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M8" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>239</v>
+      </c>
       <c r="N8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q8" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>84</v>
+      </c>
       <c r="R8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S8" s="15"/>
+        <v>240</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>241</v>
+      </c>
       <c r="T8" s="15" t="s">
-        <v>157</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="15" t="s">
-        <v>158</v>
+        <v>243</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
+      </c>
+      <c r="D9" s="15">
+        <v>10</v>
+      </c>
+      <c r="E9" s="15">
+        <v>0</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="R9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S9" s="15"/>
+        <v>53</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>244</v>
+      </c>
       <c r="T9" s="15" t="s">
-        <v>159</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="15" t="s">
-        <v>113</v>
+        <v>246</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="15">
-        <v>200</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>47</v>
+        <v>52</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="15">
+        <v>10</v>
+      </c>
+      <c r="E10" s="15">
+        <v>0</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>247</v>
+      </c>
       <c r="T10" s="15" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="15" t="s">
-        <v>161</v>
+        <v>249</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="15">
-        <v>50</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>47</v>
+        <v>52</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="15">
+        <v>10</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S11" s="15" t="s">
+        <v>250</v>
+      </c>
       <c r="T11" s="15" t="s">
-        <v>162</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="15" t="s">
-        <v>163</v>
+        <v>252</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
+      </c>
+      <c r="D12" s="15">
+        <v>10</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>164</v>
+        <v>53</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M12" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O12" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q12" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q12" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="R12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S12" s="15"/>
+        <v>53</v>
+      </c>
+      <c r="S12" s="15" t="s">
+        <v>253</v>
+      </c>
       <c r="T12" s="15" t="s">
-        <v>165</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A4:T4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:R5"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:E1" location="Clases!A1" display="&lt;-Volver al inicio" xr:uid="{EF73B532-6CCE-47D8-961A-B0B7724BE22D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6405FC-044D-47E0-A7ED-B00D2E06152E}">
+  <dimension ref="A1:T14"/>
+  <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="61.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="19.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="A1" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A2" s="2" t="str">
+        <f>Entidades!$A$1</f>
+        <v>Entidad</v>
+      </c>
+      <c r="B2" s="23" t="str">
+        <f>Entidades!A10</f>
+        <v>Cotizacion</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="24"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="3" t="str">
+        <f>Entidades!$B$1</f>
+        <v>Desripción</v>
+      </c>
+      <c r="B3" s="25" t="str">
+        <f>Entidades!B10</f>
+        <v>Entidad que contiene la información de la respuesta que da el proveedor a la solicitud de cotización del cliente</v>
+      </c>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="21"/>
+    </row>
+    <row r="5" spans="1:20" s="4" customFormat="1">
+      <c r="A5" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="T5" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="4" customFormat="1">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q6" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="15">
+        <v>36</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q7" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="S7" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="T7" s="15" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="T8" s="15" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="15">
+        <v>100</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="T9" s="15" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="T10" s="15" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="15">
+        <v>255</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S11" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="T11" s="15" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S12" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="T12" s="15" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S13" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="T13" s="15" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="15">
+        <v>36</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q14" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R14" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="S14" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="T14" s="15" t="s">
+        <v>276</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A4:T4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:R5"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1:E1" location="Clases!A1" display="&lt;-Volver al inicio" xr:uid="{D1E3B5F5-2420-4FB4-B3C3-CFBA14AAE0D4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6126429D-1B10-43E4-A762-EE4E3AFC7A2B}">
+  <dimension ref="A1:T16"/>
+  <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="61.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="19.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="A1" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A2" s="2" t="str">
+        <f>Entidades!$A$1</f>
+        <v>Entidad</v>
+      </c>
+      <c r="B2" s="23" t="str">
+        <f>Entidades!A10</f>
+        <v>Cotizacion</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="24"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="3" t="str">
+        <f>Entidades!$B$1</f>
+        <v>Desripción</v>
+      </c>
+      <c r="B3" s="25" t="str">
+        <f>Entidades!B10</f>
+        <v>Entidad que contiene la información de la respuesta que da el proveedor a la solicitud de cotización del cliente</v>
+      </c>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="21"/>
+    </row>
+    <row r="5" spans="1:20" s="4" customFormat="1">
+      <c r="A5" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="T5" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="4" customFormat="1">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q6" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="15">
+        <v>36</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q7" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="S7" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="T7" s="15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="T8" s="15" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="T9" s="15" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="T10" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="C11" s="15">
+        <v>15</v>
+      </c>
+      <c r="D11" s="15">
+        <v>2</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="P11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R11" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="S11" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="T11" s="15"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="15">
+        <v>255</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S12" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="T12" s="15" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S13" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="T13" s="15" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S14" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="T14" s="15" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="15">
+        <v>36</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P15" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q15" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R15" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="S15" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="T15" s="15" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="15">
+        <v>36</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O16" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P16" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R16" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="S16" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="T16" s="15" t="s">
+        <v>302</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="P5:R5"/>
@@ -2832,35 +5846,20 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="S5:S6"/>
     <mergeCell ref="T5:T6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1:E1" location="Clases!A1" display="&lt;-Volver al inicio" xr:uid="{D59F3A60-5BCE-40D7-B413-8AF5A83E547E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7C92F90A-A7AE-4D8C-95D0-1528BB514DB1}">
-          <x14:formula1>
-            <xm:f>Valores!$D$2:$D$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q7:Q12</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D1AF5339-95B1-4E96-B34D-410CB58EC354}">
-          <x14:formula1>
-            <xm:f>Valores!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>N7:N12 F7:I12 L7:L12 P7:P12 R8:R12</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1255403-6348-4EA1-A621-73D3E528C0B5}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -2939,12 +5938,36 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" thickBot="1">
+    <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2986,7 +6009,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" thickBot="1">
       <c r="A1" s="18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -3021,7 +6044,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -3045,52 +6068,52 @@
     </row>
     <row r="5" spans="1:20" s="4" customFormat="1">
       <c r="A5" s="17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
       <c r="S5" s="17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="4" customFormat="1">
@@ -3103,152 +6126,156 @@
       <c r="G6" s="17"/>
       <c r="H6" s="22"/>
       <c r="I6" s="14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>0</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="15" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
       <c r="L7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="S7" s="15"/>
       <c r="T7" s="15" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="15" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C8" s="15">
         <v>50</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="P8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="S8" s="15"/>
       <c r="T8" s="15" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="B5:B6"/>
@@ -3263,10 +6290,6 @@
     <mergeCell ref="I5:K5"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1:E1" location="Clases!A1" display="&lt;-Volver al inicio" xr:uid="{845DD4A4-356D-496B-892B-AFFC00460198}"/>
@@ -3304,41 +6327,41 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -3376,7 +6399,7 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -3411,7 +6434,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -3435,52 +6458,52 @@
     </row>
     <row r="5" spans="1:20" s="4" customFormat="1">
       <c r="A5" s="17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
       <c r="S5" s="17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="4" customFormat="1">
@@ -3493,207 +6516,204 @@
       <c r="G6" s="17"/>
       <c r="H6" s="22"/>
       <c r="I6" s="14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>0</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="15" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
       <c r="L7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="O7" s="15"/>
       <c r="P7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="S7" s="15"/>
       <c r="T7" s="15" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="15" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J8" s="15" t="s">
         <v>2</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M8" s="15"/>
       <c r="N8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="O8" s="15"/>
       <c r="P8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="S8" s="15"/>
       <c r="T8" s="15" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="15" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C9" s="15">
         <v>50</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
       <c r="L9" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="O9" s="15"/>
       <c r="P9" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="S9" s="15"/>
       <c r="T9" s="15" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:K5"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="P5:R5"/>
@@ -3709,6 +6729,9 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="S5:S6"/>
     <mergeCell ref="T5:T6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1:E1" location="Clases!A1" display="&lt;-Volver al inicio" xr:uid="{DD233E73-01C2-4C61-BC95-8F8D16D1DD21}"/>
@@ -3737,7 +6760,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5469456B-A845-4900-B1D7-948BA1CBAEAD}">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -3749,7 +6772,7 @@
     <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -3758,14 +6781,14 @@
     <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19" style="1" customWidth="1"/>
     <col min="20" max="20" width="42.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -3779,7 +6802,7 @@
       </c>
       <c r="B2" s="23" t="str">
         <f>Entidades!A4</f>
-        <v>Cliente</v>
+        <v>Usuario</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
@@ -3800,7 +6823,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -3824,52 +6847,52 @@
     </row>
     <row r="5" spans="1:20" s="4" customFormat="1">
       <c r="A5" s="17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
       <c r="S5" s="17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="4" customFormat="1">
@@ -3882,363 +6905,784 @@
       <c r="G6" s="17"/>
       <c r="H6" s="22"/>
       <c r="I6" s="14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>0</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="15" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>47</v>
+        <v>82</v>
+      </c>
+      <c r="C7" s="15">
+        <v>36</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="S7" s="15"/>
+        <v>83</v>
+      </c>
+      <c r="S7" s="15" t="s">
+        <v>85</v>
+      </c>
       <c r="T7" s="15" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="15" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C8" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M8" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>88</v>
+      </c>
       <c r="N8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="S8" s="15"/>
+        <v>89</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>90</v>
+      </c>
       <c r="T8" s="15" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="15" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C9" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P9" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="S9" s="15"/>
+        <v>93</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>94</v>
+      </c>
       <c r="T9" s="15" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="15">
+        <v>100</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q10" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="15">
-        <v>50</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="N10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q10" s="15" t="s">
-        <v>51</v>
-      </c>
       <c r="R10" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="S10" s="15"/>
+        <v>97</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>98</v>
+      </c>
       <c r="T10" s="15" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="15" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C11" s="15">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>101</v>
+      </c>
       <c r="N11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P11" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="S11" s="15"/>
+        <v>102</v>
+      </c>
+      <c r="S11" s="15" t="s">
+        <v>103</v>
+      </c>
       <c r="T11" s="15" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="15" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>47</v>
+        <v>60</v>
+      </c>
+      <c r="C12" s="15">
+        <v>255</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S12" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="T12" s="15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="15">
+        <v>100</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S13" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="T13" s="15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="15">
+        <v>100</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S14" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="K12" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q12" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="R12" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15" t="s">
-        <v>93</v>
+      <c r="T14" s="15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S15" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="T15" s="15" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="15">
+        <v>36</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O16" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P16" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R16" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="S16" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="T16" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="15">
+        <v>36</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O17" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P17" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R17" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="S17" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="T17" s="15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P18" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S18" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="T18" s="15" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:K5"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="P5:R5"/>
@@ -4254,29 +7698,14 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="S5:S6"/>
     <mergeCell ref="T5:T6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1:E1" location="Clases!A1" display="&lt;-Volver al inicio" xr:uid="{20417C4D-5674-41C3-B33E-E22FCE876753}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{60274396-F1D5-49D4-9E81-72621AFEE44E}">
-          <x14:formula1>
-            <xm:f>Valores!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>F7:I12 N7:N12 P7:P12 L7:L12</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6F556931-19A2-4B82-8391-C0EE34475267}">
-          <x14:formula1>
-            <xm:f>Valores!$D$2:$D$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q7:Q12</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -4303,14 +7732,14 @@
     <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20" style="1" customWidth="1"/>
     <col min="20" max="20" width="72.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -4345,7 +7774,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -4369,52 +7798,52 @@
     </row>
     <row r="5" spans="1:20" s="4" customFormat="1">
       <c r="A5" s="17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
       <c r="S5" s="17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="4" customFormat="1">
@@ -4427,258 +7856,351 @@
       <c r="G6" s="17"/>
       <c r="H6" s="22"/>
       <c r="I6" s="14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>0</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="15" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>47</v>
+        <v>82</v>
+      </c>
+      <c r="C7" s="15">
+        <v>36</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="S7" s="15"/>
+        <v>128</v>
+      </c>
+      <c r="S7" s="15" t="s">
+        <v>129</v>
+      </c>
       <c r="T7" s="15" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>47</v>
+        <v>60</v>
+      </c>
+      <c r="C8" s="15">
+        <v>150</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="S8" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>103</v>
+      </c>
       <c r="T8" s="15" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="15" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="15">
-        <v>50</v>
+        <v>113</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L9" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P9" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="S9" s="15"/>
+        <v>53</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>134</v>
+      </c>
       <c r="T9" s="15" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="15" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>47</v>
+        <v>82</v>
+      </c>
+      <c r="C10" s="15">
+        <v>36</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>81</v>
+      </c>
       <c r="L10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>84</v>
+      </c>
       <c r="R10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S10" s="15"/>
+        <v>138</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="T10" s="15" t="s">
-        <v>107</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S11" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="T11" s="15" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:K5"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="P5:R5"/>
@@ -4694,35 +8216,20 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="S5:S6"/>
     <mergeCell ref="T5:T6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1:E1" location="Clases!A1" display="&lt;-Volver al inicio" xr:uid="{5A9B0916-D784-492D-9C44-93400C1EDF3C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3C342E60-CBB7-4EBB-AA77-B3756ECD44A0}">
-          <x14:formula1>
-            <xm:f>Valores!$D$2:$D$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q7:Q10</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{433861EC-3044-4910-B707-574B1E50F763}">
-          <x14:formula1>
-            <xm:f>Valores!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>F7:I10 L7:L10 N7:N10 P7:P10 R10</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F886A707-2EEC-4CAC-ABAE-28BC69EDAA9D}">
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" style="1" bestFit="1" customWidth="1"/>
@@ -4743,14 +8250,14 @@
     <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.140625" style="1" customWidth="1"/>
     <col min="20" max="20" width="44" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -4785,7 +8292,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -4809,52 +8316,52 @@
     </row>
     <row r="5" spans="1:20" s="4" customFormat="1">
       <c r="A5" s="17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
       <c r="S5" s="17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="4" customFormat="1">
@@ -4867,301 +8374,598 @@
       <c r="G6" s="17"/>
       <c r="H6" s="22"/>
       <c r="I6" s="14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>0</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="15" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="C7" s="15">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>143</v>
+      </c>
       <c r="N7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="S7" s="15"/>
+        <v>143</v>
+      </c>
+      <c r="S7" s="15" t="s">
+        <v>144</v>
+      </c>
       <c r="T7" s="15" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="15" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C8" s="15">
         <v>50</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q8" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>84</v>
+      </c>
       <c r="R8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S8" s="15"/>
+        <v>148</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>149</v>
+      </c>
       <c r="T8" s="15" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="15" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C9" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q9" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>84</v>
+      </c>
       <c r="R9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S9" s="15"/>
+        <v>151</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="T9" s="15" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="15" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C10" s="15">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="R10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S10" s="15"/>
+        <v>53</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>154</v>
+      </c>
       <c r="T10" s="15" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="15" t="s">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>47</v>
+        <v>60</v>
+      </c>
+      <c r="C11" s="15">
+        <v>150</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="R11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S11" s="15"/>
+        <v>53</v>
+      </c>
+      <c r="S11" s="15" t="s">
+        <v>157</v>
+      </c>
       <c r="T11" s="15" t="s">
-        <v>118</v>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="15">
+        <v>36</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q12" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R12" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="S12" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="T12" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S13" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="T13" s="15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="15">
+        <v>255</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S14" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="T14" s="15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="15">
+        <v>255</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="O15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="S15" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="T15" s="15" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:K5"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="P5:R5"/>
@@ -5177,29 +8981,14 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="S5:S6"/>
     <mergeCell ref="T5:T6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1:E1" location="Clases!A1" display="&lt;-Volver al inicio" xr:uid="{35E7FB4A-2793-44D2-B54F-EE13DB50BD88}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0378A15A-551B-4C13-85EE-08ACCCEFDC68}">
-          <x14:formula1>
-            <xm:f>Valores!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>N7:N11 F7:I11 L7:L11 P7:P11 R8:R11</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D5A86211-5E03-4941-A40C-30D4963A67C6}">
-          <x14:formula1>
-            <xm:f>Valores!$D$2:$D$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q7:Q11</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -5233,7 +9022,7 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5268,7 +9057,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -5292,52 +9081,52 @@
     </row>
     <row r="5" spans="1:20" s="4" customFormat="1">
       <c r="A5" s="17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
       <c r="S5" s="17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="4" customFormat="1">
@@ -5350,305 +9139,350 @@
       <c r="G6" s="17"/>
       <c r="H6" s="22"/>
       <c r="I6" s="14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>0</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="15" t="s">
-        <v>119</v>
+      <c r="A7" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>47</v>
+        <v>82</v>
+      </c>
+      <c r="C7" s="15">
+        <v>36</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>170</v>
+      </c>
       <c r="N7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O7" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P7" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="S7" s="15"/>
+        <v>170</v>
+      </c>
+      <c r="S7" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="T7" s="15" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:20">
-      <c r="A8" s="15" t="s">
-        <v>53</v>
+      <c r="A8" s="16" t="s">
+        <v>92</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C8" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L8" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>122</v>
+        <v>173</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O8" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q8" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>84</v>
+      </c>
       <c r="R8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S8" s="15"/>
+        <v>174</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="T8" s="15" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:20">
-      <c r="A9" s="15" t="s">
-        <v>115</v>
+      <c r="A9" s="16" t="s">
+        <v>156</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C9" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q9" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="R9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S9" s="15"/>
+        <v>53</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>157</v>
+      </c>
       <c r="T9" s="15" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:20">
-      <c r="A10" s="15" t="s">
-        <v>125</v>
+      <c r="A10" s="16" t="s">
+        <v>110</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>47</v>
+        <v>60</v>
+      </c>
+      <c r="C10" s="15">
+        <v>100</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="R10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S10" s="15"/>
+        <v>53</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>4</v>
+      </c>
       <c r="T10" s="15" t="s">
-        <v>126</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:20">
-      <c r="A11" s="15" t="s">
-        <v>127</v>
+      <c r="A11" s="16" t="s">
+        <v>178</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>47</v>
+        <v>82</v>
+      </c>
+      <c r="C11" s="15">
+        <v>36</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="N11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="O11" s="15"/>
+        <v>54</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="P11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q11" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>84</v>
+      </c>
       <c r="R11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S11" s="15"/>
+        <v>180</v>
+      </c>
+      <c r="S11" s="15" t="s">
+        <v>144</v>
+      </c>
       <c r="T11" s="15" t="s">
-        <v>129</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:K5"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="P5:R5"/>
@@ -5664,42 +9498,18 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="S5:S6"/>
     <mergeCell ref="T5:T6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1:E1" location="Clases!A1" display="&lt;-Volver al inicio" xr:uid="{DFCD3E80-CC9B-40BF-8139-8D34DB51887F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3A2EE815-F167-44A8-9F17-80451869E828}">
-          <x14:formula1>
-            <xm:f>Valores!$D$2:$D$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q7:Q11</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2DCC5458-979F-47B4-9264-A407A35CA891}">
-          <x14:formula1>
-            <xm:f>Valores!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>N7:N11 F7:I11 L7:L11 P7:P11 R8:R11</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="36cf0646-7300-4608-bcc3-e29ed014863a">
@@ -5710,7 +9520,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101001945CC36234B18439988D70FCB761011" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="8ca733e0ec3c0df6e34813901e7a3ca5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="36cf0646-7300-4608-bcc3-e29ed014863a" xmlns:ns3="734bc881-a844-4d86-9741-49f87248cc41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="aed9a3083501fe1d9ea761da13b3b1bf" ns2:_="" ns3:_="">
     <xsd:import namespace="36cf0646-7300-4608-bcc3-e29ed014863a"/>
@@ -5905,16 +9715,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F878460-2F3A-41BD-95C2-4CD9C0DA2538}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AE2A7AE-CB58-44F4-8195-7E287552EB43}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AE2A7AE-CB58-44F4-8195-7E287552EB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF4E84B5-596C-454A-9A07-8478178DEDDA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFC3D22C-AA01-40DA-B474-510E989FE5B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F878460-2F3A-41BD-95C2-4CD9C0DA2538}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
